--- a/老余裸K圖表_20260625/老余裸K_賺賠比精選_20260625.xlsx
+++ b/老余裸K圖表_20260625/老余裸K_賺賠比精選_20260625.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,18 +105,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -547,109 +535,35 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>4178.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>永笙-KY</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1 : 12.45</t>
+          <t>1 : 5.19</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>323</v>
+        <v>18.15</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>313</v>
+        <v>16.6</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>447.5</v>
+        <v>26.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1464</v>
+        <v>858</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>4178.TW</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>永笙-KY</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>1 : 5.19</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>858</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3709.TWO</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>鑫聯大投控</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1 : 3.67</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>921</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -658,8 +572,6 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
